--- a/InputData/indst/IEMUEF/Indst Eqpt Min Unit E Factor.xlsx
+++ b/InputData/indst/IEMUEF/Indst Eqpt Min Unit E Factor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\IEMUEF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080B0A92-470D-40D5-8454-288F385C91B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5F0E7B8-F6D0-439F-932C-D14D66E27D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="684" firstSheet="8" activeTab="14" xr2:uid="{910269CE-FD31-46D7-B2D8-8AF36ED85333}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="684" firstSheet="8" activeTab="14" xr2:uid="{910269CE-FD31-46D7-B2D8-8AF36ED85333}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -2739,7 +2739,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="703">
   <si>
     <t>Source:</t>
   </si>
@@ -2790,12 +2790,6 @@
   </si>
   <si>
     <t>Other process</t>
-  </si>
-  <si>
-    <t>green hydrogen if</t>
-  </si>
-  <si>
-    <t>low carbon hydrogen if</t>
   </si>
   <si>
     <t xml:space="preserve">COP: </t>
@@ -4770,9 +4764,6 @@
     <t>WP4: electricity &gt;1000 °C moved from 1.187 (theoretical-minimum-to-actual ratio, 'High Temp'!G4 = 84.3%) to best-practice delivered EAF efficiency 70% → 1.429. Kirschen et al. 2009 upper bound with scrap preheat and off-gas recovery. The theoretical-minimum block on 'High Temp' is retained as documentation. Ref 30.</t>
   </si>
   <si>
-    <t>WP5: validation block added at IEMUEF rows 16-26 — every minimum factor is checked against the corresponding start-year factor (electricity and natural gas). All ten checks PASS. Headroom: electricity 35.0% / 34.4% / 13.0% / 12.3% / 22.8%; natural gas 16.5% / 19.3% / 15.5% / 46.8% / 56.6%.</t>
-  </si>
-  <si>
     <t>LHV/HHV ratio</t>
   </si>
   <si>
@@ -4900,6 +4891,9 @@
   </si>
   <si>
     <t>Status at sign-off: NO OPEN ITEMS in this file. Closed and documented above — system-boundary alignment with the start-year file (WP1-WP6, A98-A104); HHV-consistent fuel-adjustment ratios (A111); &gt;1000 °C regenerative-burner addressability, applied with the 55% iron &amp; steel share (A113); process vs equipment substitution above 1000 °C, resolved by the coking-coal-as-feedstock convention (A114); five reviewed decisions (A107); tab cleanup (A115-A116). File state: no formula errors, no external workbook links, all ten min-vs-start-year validation checks PASS. Output grid — electricity 0.200 / 0.333 / 1.103 / 1.346 / 1.429; natural gas 1.010 / 1.010 / 1.192 / 1.178 / 1.465; coal 1.136 / 1.136 / 1.146 / 1.151 / 1.445; petroleum 1.087 / 1.087 / 1.143 / 1.127 / 1.427. The corresponding revisions to the START-YEAR file are tracked in that file, not here.</t>
+  </si>
+  <si>
+    <t>WP5: validation block added at IEMUEF rows 14-24 — every minimum factor is checked against the corresponding start-year factor (electricity and natural gas). All ten checks PASS. Headroom: electricity 35.0% / 34.4% / 13.0% / 12.3% / 22.8%; natural gas 16.5% / 19.3% / 15.5% / 46.8% / 56.6%.</t>
   </si>
 </sst>
 </file>
@@ -27994,7 +27988,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -28002,12 +27996,12 @@
         <v>0</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="B4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -28017,27 +28011,27 @@
     </row>
     <row r="6" spans="1:2">
       <c r="B6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="B7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="B8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="B10" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="B11" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -28047,67 +28041,67 @@
     </row>
     <row r="13" spans="1:2">
       <c r="B13" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="B14" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="B15" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" s="53" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" s="54" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" s="53" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="26" spans="2:2">
       <c r="B26" s="15" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="28" spans="2:2">
@@ -28115,82 +28109,82 @@
     </row>
     <row r="30" spans="2:2">
       <c r="B30" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="2:2">
       <c r="B31" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="2:2">
       <c r="B37" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" spans="2:2">
       <c r="B39" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="43" spans="2:2">
       <c r="B43" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="45" spans="2:2">
       <c r="B45" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="47" spans="2:2">
       <c r="B47" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="B49" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -28200,7 +28194,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -28210,42 +28204,42 @@
     </row>
     <row r="55" spans="1:2">
       <c r="B55" s="53" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="B56" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="B57" s="5" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="B58" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="B59" s="54" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="B60" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="B62" s="53" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="B63" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -28255,27 +28249,27 @@
     </row>
     <row r="65" spans="2:2">
       <c r="B65" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" s="54" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="67" spans="2:2">
       <c r="B67" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="69" spans="2:2">
       <c r="B69" s="53" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="70" spans="2:2">
       <c r="B70" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="71" spans="2:2">
@@ -28285,197 +28279,197 @@
     </row>
     <row r="72" spans="2:2">
       <c r="B72" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="73" spans="2:2">
       <c r="B73" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="75" spans="2:2">
       <c r="B75" s="53" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="76" spans="2:2">
       <c r="B76" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="77" spans="2:2">
       <c r="B77" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="78" spans="2:2">
       <c r="B78" s="54" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="80" spans="2:2">
       <c r="B80" s="53" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="81" spans="2:2">
       <c r="B81" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="82" spans="2:2">
       <c r="B82" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="83" spans="2:2">
       <c r="B83" s="54" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="85" spans="2:2">
       <c r="B85" s="53" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="86" spans="2:2">
       <c r="B86" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="87" spans="2:2">
       <c r="B87" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="88" spans="2:2">
       <c r="B88" s="54" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="89" spans="2:2">
       <c r="B89" s="54" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="91" spans="2:2">
       <c r="B91" s="53" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="92" spans="2:2">
       <c r="B92" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="93" spans="2:2">
       <c r="B93" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="94" spans="2:2">
       <c r="B94" s="54" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="95" spans="2:2">
       <c r="B95" s="54" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="146" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="15" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="15" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="15" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="15" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="15" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="15" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="15" t="s">
-        <v>661</v>
+        <v>702</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="15" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="15" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="15" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" s="154" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="154" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="154" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" s="158" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="154" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="154" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="154" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="151" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
   </sheetData>
@@ -28495,17 +28489,17 @@
   <sheetData>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B4">
         <v>0.65200000000000002</v>
@@ -28514,7 +28508,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B5">
         <v>0.13650000000000001</v>
@@ -28523,7 +28517,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B6">
         <v>0.20050000000000001</v>
@@ -28532,7 +28526,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B7" s="17">
         <v>1.0999999999999999E-2</v>
@@ -28540,17 +28534,17 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B11" s="11">
         <v>0.9</v>
@@ -28558,7 +28552,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B12" s="11">
         <v>0.85</v>
@@ -28566,7 +28560,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B13" s="11">
         <v>0.1</v>
@@ -28574,18 +28568,18 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B14" s="11">
         <v>0.7</v>
       </c>
       <c r="C14" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B16" s="11">
         <f>B11*B4+B12*B5+B6*B14+B11*B7</f>
@@ -28594,18 +28588,18 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B18" s="11">
         <v>0.93</v>
       </c>
       <c r="C18" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B19">
         <f>1/B18</f>
@@ -28614,12 +28608,12 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -28629,7 +28623,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B25" s="11">
         <f>B18*A23</f>
@@ -28638,7 +28632,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B26">
         <f>1/B25</f>
@@ -28664,7 +28658,7 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -28684,12 +28678,12 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -28699,30 +28693,30 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="C4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D4" t="s">
         <v>151</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="E4" t="s">
         <v>152</v>
       </c>
-      <c r="C4" t="s">
-        <v>137</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>153</v>
       </c>
-      <c r="E4" t="s">
+      <c r="H4" t="s">
         <v>154</v>
-      </c>
-      <c r="F4" t="s">
-        <v>155</v>
-      </c>
-      <c r="H4" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="26" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B5" s="27">
         <v>0.30299999999999999</v>
@@ -28741,12 +28735,12 @@
         <v>19</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="25" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B6" s="27">
         <f>AVERAGE(0.35,0.305,0.266)</f>
@@ -28757,7 +28751,7 @@
         <v>3.2573289902280131</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E6">
         <v>2100</v>
@@ -28768,7 +28762,7 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B8" s="29"/>
       <c r="C8" s="29"/>
@@ -28778,18 +28772,18 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="25" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="25" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B10">
         <f>AVERAGE(0.836,0.885,0.905)</f>
@@ -28800,7 +28794,7 @@
         <v>1.1424219345011424</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E10">
         <v>2600</v>
@@ -28811,7 +28805,7 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="26" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B11">
         <f>B10*(1-AVERAGE(0.1,0.15))</f>
@@ -28823,12 +28817,12 @@
       </c>
       <c r="D11" s="28"/>
       <c r="F11" s="28" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="25" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B12">
         <f>1/C12</f>
@@ -28847,7 +28841,7 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="25" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B13">
         <f>1/C13</f>
@@ -28864,7 +28858,7 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -28874,7 +28868,7 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="25" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B16" s="14">
         <f>(AVERAGE(C5:C6)-AVERAGE(C11:C13))/AVERAGE(C5:C6)</f>
@@ -28887,13 +28881,13 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H18" s="2"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -28903,27 +28897,27 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="25" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C20" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D20" t="s">
+        <v>226</v>
+      </c>
+      <c r="E20" t="s">
         <v>228</v>
       </c>
-      <c r="E20" t="s">
-        <v>230</v>
-      </c>
       <c r="H20" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="26" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B21" s="32">
         <f>-0.041</f>
@@ -28941,12 +28935,12 @@
         <v>-8.968750000000001E-3</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -28962,109 +28956,109 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="35" spans="1:20">
       <c r="A35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D35" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="36" spans="1:20">
       <c r="A36" t="s">
+        <v>171</v>
+      </c>
+      <c r="B36" t="s">
+        <v>172</v>
+      </c>
+      <c r="D36" t="s">
         <v>173</v>
       </c>
-      <c r="B36" t="s">
+      <c r="E36" t="s">
         <v>174</v>
       </c>
-      <c r="D36" t="s">
+      <c r="F36" t="s">
         <v>175</v>
       </c>
-      <c r="E36" t="s">
+      <c r="G36" t="s">
         <v>176</v>
       </c>
-      <c r="F36" t="s">
+      <c r="H36" t="s">
         <v>177</v>
       </c>
-      <c r="G36" t="s">
+      <c r="I36" t="s">
         <v>178</v>
       </c>
-      <c r="H36" t="s">
+      <c r="J36" t="s">
         <v>179</v>
       </c>
-      <c r="I36" t="s">
+      <c r="M36" t="s">
         <v>180</v>
       </c>
-      <c r="J36" t="s">
+      <c r="P36" t="s">
         <v>181</v>
       </c>
-      <c r="M36" t="s">
+      <c r="S36" t="s">
         <v>182</v>
       </c>
-      <c r="P36" t="s">
+      <c r="T36" t="s">
         <v>183</v>
-      </c>
-      <c r="S36" t="s">
-        <v>184</v>
-      </c>
-      <c r="T36" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="37" spans="1:20">
       <c r="A37" t="s">
+        <v>184</v>
+      </c>
+      <c r="B37" t="s">
+        <v>185</v>
+      </c>
+      <c r="C37" t="s">
         <v>186</v>
       </c>
-      <c r="B37" t="s">
+      <c r="J37" t="s">
         <v>187</v>
       </c>
-      <c r="C37" t="s">
+      <c r="K37" t="s">
         <v>188</v>
       </c>
-      <c r="J37" t="s">
+      <c r="L37" t="s">
         <v>189</v>
       </c>
-      <c r="K37" t="s">
-        <v>190</v>
-      </c>
-      <c r="L37" t="s">
-        <v>191</v>
-      </c>
       <c r="M37" t="s">
+        <v>187</v>
+      </c>
+      <c r="N37" t="s">
+        <v>188</v>
+      </c>
+      <c r="O37" t="s">
         <v>189</v>
       </c>
-      <c r="N37" t="s">
-        <v>190</v>
-      </c>
-      <c r="O37" t="s">
-        <v>191</v>
-      </c>
       <c r="P37" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>188</v>
+      </c>
+      <c r="R37" t="s">
         <v>189</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>190</v>
-      </c>
-      <c r="R37" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="38" spans="1:20">
       <c r="A38" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B38" s="18">
         <f>AVERAGE(S38:S39)</f>
@@ -29175,7 +29169,7 @@
     </row>
     <row r="40" spans="1:20">
       <c r="A40" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B40" s="18">
         <f>AVERAGE(S40:S42)</f>
@@ -29327,7 +29321,7 @@
     </row>
     <row r="43" spans="1:20">
       <c r="A43" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B43" s="18">
         <f>AVERAGE(S43:S45)</f>
@@ -29466,22 +29460,22 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1">
       <c r="A1" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C1" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="E1" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>198</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -29489,16 +29483,16 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C2" s="25">
         <v>2014</v>
       </c>
       <c r="D2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -29506,16 +29500,16 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C3" s="25">
         <v>2016</v>
       </c>
       <c r="D3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -29523,16 +29517,16 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C4" s="25">
         <v>2020</v>
       </c>
       <c r="D4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -29540,16 +29534,16 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C5" s="25">
         <v>2022</v>
       </c>
       <c r="D5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -29557,16 +29551,16 @@
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C6" s="25">
         <v>2021</v>
       </c>
       <c r="D6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -29574,16 +29568,16 @@
         <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C7" s="25">
         <v>2018</v>
       </c>
       <c r="D7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -29591,16 +29585,16 @@
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C8" s="25">
         <v>2015</v>
       </c>
       <c r="D8" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -29608,16 +29602,16 @@
         <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C9" s="25">
         <v>2025</v>
       </c>
       <c r="D9" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -29625,19 +29619,19 @@
         <v>27</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C10" s="25">
         <v>2004</v>
       </c>
       <c r="D10" s="15" t="s">
+        <v>625</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>626</v>
+      </c>
+      <c r="F10" s="15" t="s">
         <v>627</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>628</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -29645,19 +29639,19 @@
         <v>28</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C11" s="25">
         <v>2015</v>
       </c>
       <c r="D11" s="15" t="s">
+        <v>628</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>629</v>
+      </c>
+      <c r="F11" s="15" t="s">
         <v>630</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>631</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -29665,19 +29659,19 @@
         <v>29</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C12" s="25">
         <v>2019</v>
       </c>
       <c r="D12" s="15" t="s">
+        <v>632</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>633</v>
+      </c>
+      <c r="F12" s="15" t="s">
         <v>634</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>635</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -29685,19 +29679,19 @@
         <v>30</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C13" s="25">
         <v>2009</v>
       </c>
       <c r="D13" s="15" t="s">
+        <v>636</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>637</v>
+      </c>
+      <c r="F13" s="15" t="s">
         <v>638</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>639</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -29705,19 +29699,19 @@
         <v>31</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C14" s="25">
         <v>2012</v>
       </c>
       <c r="D14" s="15" t="s">
+        <v>640</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>641</v>
+      </c>
+      <c r="F14" s="15" t="s">
         <v>642</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>643</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -29725,19 +29719,19 @@
         <v>32</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C15" s="25">
         <v>2016</v>
       </c>
       <c r="D15" s="15" t="s">
+        <v>644</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>645</v>
+      </c>
+      <c r="F15" s="15" t="s">
         <v>646</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>647</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -29745,19 +29739,19 @@
         <v>33</v>
       </c>
       <c r="B16" s="15" t="s">
+        <v>647</v>
+      </c>
+      <c r="C16" s="153" t="s">
+        <v>648</v>
+      </c>
+      <c r="D16" s="15" t="s">
         <v>649</v>
       </c>
-      <c r="C16" s="153" t="s">
+      <c r="E16" s="15" t="s">
         <v>650</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="F16" s="15" t="s">
         <v>651</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>652</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -29765,19 +29759,19 @@
         <v>34</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C17" s="25">
         <v>2023</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
   </sheetData>
@@ -29813,7 +29807,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="33" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
@@ -29825,27 +29819,27 @@
     </row>
     <row r="2" spans="1:8" ht="30">
       <c r="A2" s="35" t="s">
+        <v>258</v>
+      </c>
+      <c r="B2" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="35" t="s">
+        <v>259</v>
+      </c>
+      <c r="D2" s="36" t="s">
         <v>260</v>
       </c>
-      <c r="B2" s="35" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="35" t="s">
-        <v>261</v>
-      </c>
-      <c r="D2" s="36" t="s">
-        <v>262</v>
-      </c>
       <c r="E2" s="45" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="F2" s="45" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D3" s="12">
         <f>(E3/$E$5)*(1-F3)</f>
@@ -29860,7 +29854,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D4" s="12">
         <f>(E4/$E$5)*(1-F4)</f>
@@ -29875,7 +29869,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D5" s="12">
         <f>(E5/$E$5)*(1-F5)</f>
@@ -29890,7 +29884,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="35" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B7" s="37"/>
       <c r="C7" s="37"/>
@@ -29902,65 +29896,65 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="16" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B10" s="110">
         <v>0.99</v>
       </c>
       <c r="C10" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B11" s="110">
         <v>0.92</v>
       </c>
       <c r="C11" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B12" s="110">
         <v>0.88</v>
       </c>
       <c r="C12" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="45" customHeight="1">
       <c r="A40" s="162" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B40" s="162"/>
       <c r="C40" s="162"/>
@@ -29968,24 +29962,24 @@
     </row>
     <row r="42" spans="1:5" ht="30">
       <c r="A42" s="38" t="s">
+        <v>271</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="C42" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="B42" s="10" t="s">
+      <c r="D42" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="C42" s="10" t="s">
+      <c r="E42" s="38" t="s">
         <v>275</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="E42" s="38" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B43">
         <v>200</v>
@@ -29997,12 +29991,12 @@
         <v>0.85</v>
       </c>
       <c r="E43" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B44">
         <v>300</v>
@@ -30016,7 +30010,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B45">
         <v>600</v>
@@ -30030,7 +30024,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B46">
         <v>1400</v>
@@ -30044,7 +30038,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B47">
         <v>2600</v>
@@ -30058,7 +30052,7 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="35" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B49" s="37"/>
       <c r="C49" s="37"/>
@@ -30066,21 +30060,21 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="38" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B50" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="D50" s="10" t="s">
         <v>285</v>
-      </c>
-      <c r="C50" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="D50" s="10" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B51" s="14">
         <f>D43*$D$3</f>
@@ -30097,7 +30091,7 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B52" s="14">
         <f>D44*$D$3</f>
@@ -30114,7 +30108,7 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B53" s="14">
         <f>D45*$D$3</f>
@@ -30131,7 +30125,7 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B54" s="14">
         <f>D46*$D$3</f>
@@ -30148,7 +30142,7 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B55" s="14">
         <f>D47*$D$3</f>
@@ -30165,7 +30159,7 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="33" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B57" s="34"/>
       <c r="C57" s="34"/>
@@ -30177,7 +30171,7 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="35" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B58" s="35"/>
       <c r="C58" s="35"/>
@@ -30185,37 +30179,37 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="16" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -30227,21 +30221,21 @@
     </row>
     <row r="88" spans="1:5" ht="30">
       <c r="A88" s="40" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B88" s="41" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C88" s="41" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D88" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B89" s="42">
         <v>90</v>
@@ -30257,7 +30251,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B90" s="42">
         <v>150</v>
@@ -30273,7 +30267,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B91" s="42">
         <v>350</v>
@@ -30289,7 +30283,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B92" s="42">
         <v>750</v>
@@ -30305,7 +30299,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B93" s="42">
         <v>1500</v>
@@ -30328,7 +30322,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="35" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B95" s="37"/>
       <c r="C95" s="37"/>
@@ -30337,21 +30331,21 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="38" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B96" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="C96" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="D96" s="10" t="s">
         <v>285</v>
-      </c>
-      <c r="C96" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="D96" s="10" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B97" s="14">
         <f>$B$12</f>
@@ -30366,12 +30360,12 @@
         <v>0.99</v>
       </c>
       <c r="E97" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B98" s="14">
         <f>$B$12</f>
@@ -30386,12 +30380,12 @@
         <v>0.99</v>
       </c>
       <c r="E98" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B99" s="14">
         <f>C91*$D$3</f>
@@ -30408,7 +30402,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B100" s="14">
         <f>D92*$D$3</f>
@@ -30423,12 +30417,12 @@
         <v>0.87890000000000001</v>
       </c>
       <c r="E100" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B101" s="14">
         <f>D93*$D$3</f>
@@ -30443,12 +30437,12 @@
         <v>0.752</v>
       </c>
       <c r="E101" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="45" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B103" s="46"/>
       <c r="C103" s="46"/>
@@ -30457,24 +30451,24 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B104" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C104" s="47" t="s">
+        <v>284</v>
+      </c>
+      <c r="D104" s="47" t="s">
         <v>285</v>
       </c>
-      <c r="C104" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="D104" s="47" t="s">
-        <v>287</v>
-      </c>
       <c r="E104" s="47" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B105" s="11">
         <f>$E105*B97+(1-$E105)*B51</f>
@@ -30494,7 +30488,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B106" s="11">
         <f t="shared" ref="B106:D106" si="0">$E106*B98+(1-$E106)*B52</f>
@@ -30514,7 +30508,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B107" s="11">
         <f>$B$134*$B$131+(1-$B$134)*($E107*B99+(1-$E107)*B53)*$B$138</f>
@@ -30534,7 +30528,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B108" s="11">
         <f>($E108*B100+(1-$E108)*B54)*$B$139</f>
@@ -30554,7 +30548,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B109" s="23">
         <f>$B$148*($E109*B101+(1-$E109)*B55)+(1-$B$148)*$B$150</f>
@@ -30574,52 +30568,52 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="45" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="109" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="53" t="s">
+        <v>425</v>
+      </c>
+      <c r="B119" s="107" t="s">
+        <v>426</v>
+      </c>
+      <c r="C119" s="107" t="s">
         <v>427</v>
       </c>
-      <c r="B119" s="107" t="s">
+      <c r="D119" s="107" t="s">
         <v>428</v>
       </c>
-      <c r="C119" s="107" t="s">
+      <c r="E119" s="107" t="s">
         <v>429</v>
       </c>
-      <c r="D119" s="107" t="s">
-        <v>430</v>
-      </c>
-      <c r="E119" s="107" t="s">
-        <v>431</v>
-      </c>
       <c r="G119" s="107" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B120" s="18">
         <f>B89</f>
@@ -30638,19 +30632,19 @@
         <v>1.0263779123473262</v>
       </c>
       <c r="F120" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="G120" s="12">
         <f>1/$B$10</f>
         <v>1.0101010101010102</v>
       </c>
       <c r="H120" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B121" s="18">
         <f>B90</f>
@@ -30669,19 +30663,19 @@
         <v>1.0405827263267431</v>
       </c>
       <c r="F121" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="G121" s="12">
         <f>1/$B$10</f>
         <v>1.0101010101010102</v>
       </c>
       <c r="H121" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B122" s="18">
         <f>B91</f>
@@ -30700,19 +30694,19 @@
         <v>1.0919414719371043</v>
       </c>
       <c r="F122" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="G122" s="12">
         <f>1/C91</f>
         <v>1.0919414719371043</v>
       </c>
       <c r="H122" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B123" s="18">
         <f>B92</f>
@@ -30731,19 +30725,19 @@
         <v>1.1377858686995108</v>
       </c>
       <c r="F123" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="G123" s="12">
         <f>1/D92</f>
         <v>1.1377858686995108</v>
       </c>
       <c r="H123" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B124" s="18">
         <f>B93</f>
@@ -30762,35 +30756,35 @@
         <v>1.3297872340425532</v>
       </c>
       <c r="F124" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="G124" s="12">
         <f>1/D93</f>
         <v>1.3297872340425532</v>
       </c>
       <c r="H124" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" s="146" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" s="147" t="s">
+        <v>593</v>
+      </c>
+      <c r="B128" s="107" t="s">
+        <v>594</v>
+      </c>
+      <c r="C128" s="147" t="s">
         <v>595</v>
-      </c>
-      <c r="B128" s="107" t="s">
-        <v>596</v>
-      </c>
-      <c r="C128" s="147" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="15" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B129" s="110">
         <v>0.05</v>
@@ -30798,7 +30792,7 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="15" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B130" s="110">
         <v>0.90300000000000002</v>
@@ -30812,7 +30806,7 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="15" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B131" s="23">
         <f>B130*(1-$B$129)</f>
@@ -30821,7 +30815,7 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="15" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B132" s="23">
         <f>C130*(1-$B$129)</f>
@@ -30830,7 +30824,7 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="15" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B133" s="23">
         <f>D130*(1-$B$129)</f>
@@ -30839,7 +30833,7 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="15" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B134" s="110">
         <v>0.55000000000000004</v>
@@ -30847,7 +30841,7 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="15" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B135" s="113">
         <f>'indst heat consumption'!K6+'indst heat consumption'!K12+'indst heat consumption'!K13+'indst heat consumption'!K14</f>
@@ -30856,7 +30850,7 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="15" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B136" s="113">
         <f>'indst heat consumption'!L6+'indst heat consumption'!L12+'indst heat consumption'!L13+'indst heat consumption'!L14</f>
@@ -30865,7 +30859,7 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="15" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B137" s="113">
         <f>'Electric Process Heat'!D7/'Heat pumps'!H25</f>
@@ -30874,7 +30868,7 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="15" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B138" s="23">
         <f>B135+(1-B135)*$B$137</f>
@@ -30883,7 +30877,7 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="15" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B139" s="23">
         <f>B136+(1-B136)*$B$137</f>
@@ -30892,31 +30886,31 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="148" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="146" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="150" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="B143" s="150" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C143" s="150" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="D143" s="150" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="15" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="B144" s="113">
         <f>'indst heat consumption'!M15</f>
@@ -30926,12 +30920,12 @@
         <v>1</v>
       </c>
       <c r="D144" s="15" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="15" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B145" s="113">
         <f>'indst heat consumption'!M19+'indst heat consumption'!M18</f>
@@ -30941,12 +30935,12 @@
         <v>1</v>
       </c>
       <c r="D145" s="15" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="15" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="B146" s="113">
         <f>'indst heat consumption'!M17</f>
@@ -30956,12 +30950,12 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="D146" s="15" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="15" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="B147" s="113">
         <f>'indst heat consumption'!M16</f>
@@ -30971,12 +30965,12 @@
         <v>0</v>
       </c>
       <c r="D147" s="15" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="150" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="B148" s="157">
         <f>SUMPRODUCT(B144:B147,C144:C147)/SUM(B144:B147)</f>
@@ -30985,12 +30979,12 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="150" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="15" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B150" s="120">
         <v>0.6</v>
@@ -30998,7 +30992,7 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="15" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B151" s="23">
         <f>D109</f>
@@ -31007,7 +31001,7 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="15" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="B152" s="12">
         <f>1/B151</f>
@@ -31016,7 +31010,7 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="15" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B153" s="149">
         <v>1.3297872340425501</v>
@@ -31024,22 +31018,22 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="154" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="154" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="146" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="15" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="B158" s="111">
         <v>0</v>
@@ -31047,7 +31041,7 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="15" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="B159" s="23">
         <f>B147</f>
@@ -31056,7 +31050,7 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="150" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B160" s="157">
         <f>B158+B159</f>
@@ -31065,7 +31059,7 @@
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="15" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B161" s="23">
         <f>1-B160</f>
@@ -31074,7 +31068,7 @@
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="158" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
     </row>
   </sheetData>
@@ -31102,22 +31096,22 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30">
       <c r="A1" s="49" t="s">
+        <v>297</v>
+      </c>
+      <c r="B1" s="49" t="s">
+        <v>298</v>
+      </c>
+      <c r="C1" s="49" t="s">
         <v>299</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="D1" s="49" t="s">
         <v>300</v>
       </c>
-      <c r="C1" s="49" t="s">
+      <c r="E1" s="49" t="s">
         <v>301</v>
       </c>
-      <c r="D1" s="49" t="s">
+      <c r="F1" s="49" t="s">
         <v>302</v>
-      </c>
-      <c r="E1" s="49" t="s">
-        <v>303</v>
-      </c>
-      <c r="F1" s="49" t="s">
-        <v>304</v>
       </c>
       <c r="H1" s="50" t="s">
         <v>0</v>
@@ -31143,7 +31137,7 @@
         <v>0.99950000000000006</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -31189,7 +31183,7 @@
         <v>0.99780000000000002</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -31212,7 +31206,7 @@
         <v>0.997</v>
       </c>
       <c r="H5" s="51" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -34170,7 +34164,7 @@
   <sheetPr>
     <tabColor theme="3" tint="0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="45" bestFit="1" customWidth="1"/>
@@ -34182,19 +34176,19 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1" t="s">
         <v>288</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>289</v>
       </c>
-      <c r="D1" t="s">
-        <v>290</v>
-      </c>
-      <c r="E1" t="s">
-        <v>291</v>
-      </c>
       <c r="F1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G1" t="s">
         <v>14</v>
@@ -34206,13 +34200,13 @@
         <v>16</v>
       </c>
       <c r="J1" t="s">
+        <v>249</v>
+      </c>
+      <c r="K1" t="s">
+        <v>250</v>
+      </c>
+      <c r="L1" t="s">
         <v>251</v>
-      </c>
-      <c r="K1" t="s">
-        <v>252</v>
-      </c>
-      <c r="L1" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -34346,11 +34340,11 @@
         <v>2.1414913957934991</v>
       </c>
       <c r="I4" s="12">
-        <f t="shared" ref="I4:I13" si="0">I3</f>
+        <f t="shared" ref="I4:I11" si="0">I3</f>
         <v>1.4084507042253522</v>
       </c>
       <c r="J4" s="12">
-        <f t="shared" ref="J4:J13" si="1">B4</f>
+        <f t="shared" ref="J4:J11" si="1">B4</f>
         <v>1.0101010101010102</v>
       </c>
       <c r="K4" s="12">
@@ -34358,7 +34352,7 @@
         <v>2.6881720430107525</v>
       </c>
       <c r="L4" s="12">
-        <f t="shared" ref="L4:L13" si="2">$L$3</f>
+        <f t="shared" ref="L4:L11" si="2">$L$3</f>
         <v>2.5249452352579165</v>
       </c>
     </row>
@@ -34704,326 +34698,228 @@
         <v>2.5249452352579165</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
-      <c r="A12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="12">
-        <f>1/'Combustion Efficiency'!D105</f>
-        <v>1.0101010101010102</v>
-      </c>
-      <c r="C12" s="12">
-        <f>1/'Combustion Efficiency'!D106</f>
-        <v>1.0101010101010102</v>
-      </c>
-      <c r="D12" s="12">
-        <f>1/'Combustion Efficiency'!D107</f>
-        <v>1.1918013258349178</v>
-      </c>
-      <c r="E12" s="12">
-        <f>1/'Combustion Efficiency'!D108</f>
-        <v>1.1781943590444868</v>
-      </c>
-      <c r="F12" s="12">
-        <f>1/'Combustion Efficiency'!D109</f>
-        <v>1.4653799042823039</v>
-      </c>
-      <c r="G12" s="12">
-        <f>Cooling!$K$4</f>
-        <v>0.7246376811594204</v>
-      </c>
-      <c r="H12" s="12">
-        <f>'Machine Drive'!$J$36</f>
-        <v>2.1414913957934991</v>
-      </c>
-      <c r="I12" s="12">
-        <f t="shared" si="0"/>
-        <v>1.4084507042253522</v>
-      </c>
-      <c r="J12" s="12">
-        <f t="shared" si="1"/>
-        <v>1.0101010101010102</v>
-      </c>
-      <c r="K12" s="12">
-        <f>Lighting!$B$26</f>
-        <v>2.6881720430107525</v>
-      </c>
-      <c r="L12" s="12">
-        <f t="shared" si="2"/>
-        <v>2.5249452352579165</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="12">
-        <f>1/'Combustion Efficiency'!D105</f>
-        <v>1.0101010101010102</v>
-      </c>
-      <c r="C13" s="12">
-        <f>1/'Combustion Efficiency'!D106</f>
-        <v>1.0101010101010102</v>
-      </c>
-      <c r="D13" s="12">
-        <f>1/'Combustion Efficiency'!D107</f>
-        <v>1.1918013258349178</v>
-      </c>
-      <c r="E13" s="12">
-        <f>1/'Combustion Efficiency'!D108</f>
-        <v>1.1781943590444868</v>
-      </c>
-      <c r="F13" s="12">
-        <f>1/'Combustion Efficiency'!D109</f>
-        <v>1.4653799042823039</v>
-      </c>
-      <c r="G13" s="12">
-        <f>Cooling!$K$4</f>
-        <v>0.7246376811594204</v>
-      </c>
-      <c r="H13" s="12">
-        <f>'Machine Drive'!$J$36</f>
-        <v>2.1414913957934991</v>
-      </c>
-      <c r="I13" s="12">
-        <f t="shared" si="0"/>
-        <v>1.4084507042253522</v>
-      </c>
-      <c r="J13" s="12">
-        <f t="shared" si="1"/>
-        <v>1.0101010101010102</v>
-      </c>
-      <c r="K13" s="12">
-        <f>Lighting!$B$26</f>
-        <v>2.6881720430107525</v>
-      </c>
-      <c r="L13" s="12">
-        <f t="shared" si="2"/>
-        <v>2.5249452352579165</v>
+    <row r="14" spans="1:12">
+      <c r="A14" s="146" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="148" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="146" t="s">
+      <c r="A16" s="147" t="s">
         <v>617</v>
       </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="148" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="147" t="s">
-        <v>619</v>
-      </c>
-      <c r="B18" s="107" t="str">
-        <f t="shared" ref="B18:F19" si="3">B1</f>
+      <c r="B16" s="107" t="str">
+        <f t="shared" ref="B16:F17" si="3">B1</f>
         <v>&lt;100 °C</v>
       </c>
-      <c r="C18" s="107" t="str">
+      <c r="C16" s="107" t="str">
         <f t="shared" si="3"/>
         <v>100-200 °C</v>
       </c>
-      <c r="D18" s="107" t="str">
+      <c r="D16" s="107" t="str">
         <f t="shared" si="3"/>
         <v>200-500 °C</v>
       </c>
-      <c r="E18" s="107" t="str">
+      <c r="E16" s="107" t="str">
         <f t="shared" si="3"/>
         <v>500-1000 °C</v>
       </c>
-      <c r="F18" s="107" t="str">
+      <c r="F16" s="107" t="str">
         <f t="shared" si="3"/>
         <v>&gt;1000 °C</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="15" t="s">
+        <v>618</v>
+      </c>
+      <c r="B17" s="12">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
+      </c>
+      <c r="C17" s="12">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D17" s="12">
+        <f t="shared" si="3"/>
+        <v>1.103417836749331</v>
+      </c>
+      <c r="E17" s="12">
+        <f t="shared" si="3"/>
+        <v>1.3458950201884252</v>
+      </c>
+      <c r="F17" s="12">
+        <f t="shared" si="3"/>
+        <v>1.4285714285714286</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="15" t="s">
+        <v>619</v>
+      </c>
+      <c r="B18" s="149">
+        <v>0.27</v>
+      </c>
+      <c r="C18" s="149">
+        <v>0.44800000000000001</v>
+      </c>
+      <c r="D18" s="149">
+        <v>1.2470000000000001</v>
+      </c>
+      <c r="E18" s="149">
+        <v>1.512</v>
+      </c>
+      <c r="F18" s="149">
+        <v>1.754</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="15" t="s">
         <v>620</v>
       </c>
-      <c r="B19" s="12">
-        <f t="shared" si="3"/>
-        <v>0.2</v>
-      </c>
-      <c r="C19" s="12">
-        <f t="shared" si="3"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D19" s="12">
-        <f t="shared" si="3"/>
-        <v>1.103417836749331</v>
-      </c>
-      <c r="E19" s="12">
-        <f t="shared" si="3"/>
-        <v>1.3458950201884252</v>
-      </c>
-      <c r="F19" s="12">
-        <f t="shared" si="3"/>
-        <v>1.4285714285714286</v>
+      <c r="B19" s="152" t="str">
+        <f>IF(B17&lt;=B18,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="C19" s="152" t="str">
+        <f>IF(C17&lt;=C18,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="D19" s="152" t="str">
+        <f>IF(D17&lt;=D18,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="E19" s="152" t="str">
+        <f>IF(E17&lt;=E18,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="F19" s="152" t="str">
+        <f>IF(F17&lt;=F18,"PASS","FAIL")</f>
+        <v>PASS</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="15" t="s">
         <v>621</v>
       </c>
-      <c r="B20" s="149">
-        <v>0.27</v>
-      </c>
-      <c r="C20" s="149">
-        <v>0.44800000000000001</v>
-      </c>
-      <c r="D20" s="149">
-        <v>1.2470000000000001</v>
-      </c>
-      <c r="E20" s="149">
-        <v>1.512</v>
-      </c>
-      <c r="F20" s="149">
-        <v>1.754</v>
+      <c r="B20" s="23">
+        <f>B18/B17-1</f>
+        <v>0.35000000000000009</v>
+      </c>
+      <c r="C20" s="23">
+        <f>C18/C17-1</f>
+        <v>0.34400000000000008</v>
+      </c>
+      <c r="D20" s="23">
+        <f>D18/D17-1</f>
+        <v>0.13012492500000006</v>
+      </c>
+      <c r="E20" s="23">
+        <f>E18/E17-1</f>
+        <v>0.12341599999999997</v>
+      </c>
+      <c r="F20" s="23">
+        <f>F18/F17-1</f>
+        <v>0.2278</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="15" t="s">
         <v>622</v>
       </c>
-      <c r="B21" s="152" t="str">
-        <f>IF(B19&lt;=B20,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-      <c r="C21" s="152" t="str">
-        <f>IF(C19&lt;=C20,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-      <c r="D21" s="152" t="str">
-        <f>IF(D19&lt;=D20,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-      <c r="E21" s="152" t="str">
-        <f>IF(E19&lt;=E20,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-      <c r="F21" s="152" t="str">
-        <f>IF(F19&lt;=F20,"PASS","FAIL")</f>
-        <v>PASS</v>
+      <c r="B21" s="12">
+        <f>B4</f>
+        <v>1.0101010101010102</v>
+      </c>
+      <c r="C21" s="12">
+        <f>C4</f>
+        <v>1.0101010101010102</v>
+      </c>
+      <c r="D21" s="12">
+        <f>D4</f>
+        <v>1.1918013258349178</v>
+      </c>
+      <c r="E21" s="12">
+        <f>E4</f>
+        <v>1.1781943590444868</v>
+      </c>
+      <c r="F21" s="12">
+        <f>F4</f>
+        <v>1.4653799042823039</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="15" t="s">
         <v>623</v>
       </c>
-      <c r="B22" s="23">
-        <f>B20/B19-1</f>
-        <v>0.35000000000000009</v>
-      </c>
-      <c r="C22" s="23">
-        <f>C20/C19-1</f>
-        <v>0.34400000000000008</v>
-      </c>
-      <c r="D22" s="23">
-        <f>D20/D19-1</f>
-        <v>0.13012492500000006</v>
-      </c>
-      <c r="E22" s="23">
-        <f>E20/E19-1</f>
-        <v>0.12341599999999997</v>
-      </c>
-      <c r="F22" s="23">
-        <f>F20/F19-1</f>
-        <v>0.2278</v>
+      <c r="B22" s="149">
+        <v>1.1764705882352942</v>
+      </c>
+      <c r="C22" s="149">
+        <v>1.2048192771084338</v>
+      </c>
+      <c r="D22" s="149">
+        <v>1.3769693936950533</v>
+      </c>
+      <c r="E22" s="149">
+        <v>1.7299035780390835</v>
+      </c>
+      <c r="F22" s="149">
+        <v>2.0438738318980092</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="15" t="s">
-        <v>624</v>
-      </c>
-      <c r="B23" s="12">
-        <f>B4</f>
-        <v>1.0101010101010102</v>
-      </c>
-      <c r="C23" s="12">
-        <f>C4</f>
-        <v>1.0101010101010102</v>
-      </c>
-      <c r="D23" s="12">
-        <f>D4</f>
-        <v>1.1918013258349178</v>
-      </c>
-      <c r="E23" s="12">
-        <f>E4</f>
-        <v>1.1781943590444868</v>
-      </c>
-      <c r="F23" s="12">
-        <f>F4</f>
-        <v>1.4653799042823039</v>
+        <v>620</v>
+      </c>
+      <c r="B23" s="152" t="str">
+        <f>IF(B21&lt;=B22,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="C23" s="152" t="str">
+        <f>IF(C21&lt;=C22,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="D23" s="152" t="str">
+        <f>IF(D21&lt;=D22,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="E23" s="152" t="str">
+        <f>IF(E21&lt;=E22,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="F23" s="152" t="str">
+        <f>IF(F21&lt;=F22,"PASS","FAIL")</f>
+        <v>PASS</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="15" t="s">
-        <v>625</v>
-      </c>
-      <c r="B24" s="149">
-        <v>1.1764705882352942</v>
-      </c>
-      <c r="C24" s="149">
-        <v>1.2048192771084338</v>
-      </c>
-      <c r="D24" s="149">
-        <v>1.3769693936950533</v>
-      </c>
-      <c r="E24" s="149">
-        <v>1.7299035780390835</v>
-      </c>
-      <c r="F24" s="149">
-        <v>2.0438738318980092</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="15" t="s">
-        <v>622</v>
-      </c>
-      <c r="B25" s="152" t="str">
-        <f>IF(B23&lt;=B24,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-      <c r="C25" s="152" t="str">
-        <f>IF(C23&lt;=C24,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-      <c r="D25" s="152" t="str">
-        <f>IF(D23&lt;=D24,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-      <c r="E25" s="152" t="str">
-        <f>IF(E23&lt;=E24,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-      <c r="F25" s="152" t="str">
-        <f>IF(F23&lt;=F24,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="15" t="s">
-        <v>623</v>
-      </c>
-      <c r="B26" s="23">
-        <f>B24/B23-1</f>
+        <v>621</v>
+      </c>
+      <c r="B24" s="23">
+        <f>B22/B21-1</f>
         <v>0.16470588235294104</v>
       </c>
-      <c r="C26" s="23">
-        <f>C24/C23-1</f>
+      <c r="C24" s="23">
+        <f>C22/C21-1</f>
         <v>0.19277108433734935</v>
       </c>
-      <c r="D26" s="23">
-        <f>D24/D23-1</f>
+      <c r="D24" s="23">
+        <f>D22/D21-1</f>
         <v>0.15536823449194914</v>
       </c>
-      <c r="E26" s="23">
-        <f>E24/E23-1</f>
+      <c r="E24" s="23">
+        <f>E22/E21-1</f>
         <v>0.46826672930434987</v>
       </c>
-      <c r="F26" s="23">
-        <f>F24/F23-1</f>
+      <c r="F24" s="23">
+        <f>F22/F21-1</f>
         <v>0.39477402817191831</v>
       </c>
     </row>
@@ -35044,7 +34940,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75">
       <c r="A1" s="114" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B1" s="115"/>
       <c r="C1" s="115"/>
@@ -35055,7 +34951,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="116" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B2" s="115"/>
       <c r="C2" s="115"/>
@@ -35075,7 +34971,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="117" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B4" s="118"/>
       <c r="C4" s="118"/>
@@ -35086,28 +34982,28 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="53" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B5" s="119" t="s">
+        <v>503</v>
+      </c>
+      <c r="C5" s="119" t="s">
+        <v>504</v>
+      </c>
+      <c r="D5" s="119" t="s">
         <v>505</v>
       </c>
-      <c r="C5" s="119" t="s">
+      <c r="E5" s="53" t="s">
         <v>506</v>
       </c>
-      <c r="D5" s="119" t="s">
-        <v>507</v>
-      </c>
-      <c r="E5" s="53" t="s">
-        <v>508</v>
-      </c>
       <c r="F5" s="119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G5" s="115"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="115" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B6" s="120">
         <v>0.97</v>
@@ -35119,16 +35015,16 @@
         <v>0.99</v>
       </c>
       <c r="E6" s="115" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="F6" s="115" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="G6" s="115"/>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="115" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B7" s="120">
         <v>0.8</v>
@@ -35140,16 +35036,16 @@
         <v>0.88</v>
       </c>
       <c r="E7" s="115" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="F7" s="115" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="G7" s="115"/>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="115" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B8" s="111">
         <v>0.67500000000000004</v>
@@ -35161,16 +35057,16 @@
         <v>0.76</v>
       </c>
       <c r="E8" s="115" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="F8" s="115" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="G8" s="115"/>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="115" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B9" s="111">
         <v>0.65</v>
@@ -35182,16 +35078,16 @@
         <v>0.7</v>
       </c>
       <c r="E9" s="115" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="F9" s="115" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="G9" s="115"/>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="115" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B10" s="111">
         <v>0.6</v>
@@ -35203,10 +35099,10 @@
         <v>0.9</v>
       </c>
       <c r="E10" s="115" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F10" s="115" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="G10" s="115"/>
     </row>
@@ -35221,7 +35117,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="117" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B12" s="118"/>
       <c r="C12" s="118"/>
@@ -35232,7 +35128,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="116" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B13" s="115"/>
       <c r="C13" s="115"/>
@@ -35243,30 +35139,30 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="53" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B14" s="119" t="s">
+        <v>524</v>
+      </c>
+      <c r="C14" s="119" t="s">
+        <v>525</v>
+      </c>
+      <c r="D14" s="119" t="s">
         <v>526</v>
       </c>
-      <c r="C14" s="119" t="s">
+      <c r="E14" s="119" t="s">
         <v>527</v>
       </c>
-      <c r="D14" s="119" t="s">
+      <c r="F14" s="119" t="s">
         <v>528</v>
       </c>
-      <c r="E14" s="119" t="s">
+      <c r="G14" s="119" t="s">
         <v>529</v>
-      </c>
-      <c r="F14" s="119" t="s">
-        <v>530</v>
-      </c>
-      <c r="G14" s="119" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="115" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B15" s="121">
         <f>'Combustion Efficiency'!B134</f>
@@ -35292,7 +35188,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="115" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B16" s="110">
         <v>0</v>
@@ -35325,7 +35221,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="117" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B18" s="118"/>
       <c r="C18" s="118"/>
@@ -35336,30 +35232,30 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="53" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B19" s="119" t="s">
+        <v>531</v>
+      </c>
+      <c r="C19" s="119" t="s">
+        <v>532</v>
+      </c>
+      <c r="D19" s="119" t="s">
         <v>533</v>
       </c>
-      <c r="C19" s="119" t="s">
+      <c r="E19" s="119" t="s">
         <v>534</v>
       </c>
-      <c r="D19" s="119" t="s">
+      <c r="F19" s="119" t="s">
         <v>535</v>
       </c>
-      <c r="E19" s="119" t="s">
+      <c r="G19" s="119" t="s">
         <v>536</v>
-      </c>
-      <c r="F19" s="119" t="s">
-        <v>537</v>
-      </c>
-      <c r="G19" s="119" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="115" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B20" s="156">
         <v>0.80198000000000003</v>
@@ -35386,7 +35282,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="115" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B21" s="156">
         <v>0.66125</v>
@@ -35422,7 +35318,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="117" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B23" s="118"/>
       <c r="C23" s="118"/>
@@ -35433,7 +35329,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="116" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B24" s="115"/>
       <c r="C24" s="115"/>
@@ -35444,26 +35340,26 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="53" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B25" s="119" t="s">
+        <v>539</v>
+      </c>
+      <c r="C25" s="119" t="s">
+        <v>540</v>
+      </c>
+      <c r="D25" s="119" t="s">
         <v>541</v>
       </c>
-      <c r="C25" s="119" t="s">
+      <c r="E25" s="119" t="s">
         <v>542</v>
-      </c>
-      <c r="D25" s="119" t="s">
-        <v>543</v>
-      </c>
-      <c r="E25" s="119" t="s">
-        <v>544</v>
       </c>
       <c r="F25" s="115"/>
       <c r="G25" s="115"/>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="115" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B26" s="156">
         <v>0.73780000000000001</v>
@@ -35484,7 +35380,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="115" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B27" s="156">
         <v>0.49349999999999999</v>
@@ -35514,7 +35410,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B29" s="115"/>
       <c r="C29" s="115"/>
@@ -35525,7 +35421,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="128" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B30" s="115"/>
       <c r="C30" s="115"/>
@@ -35536,7 +35432,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="112" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B31" s="115"/>
       <c r="C31" s="115"/>
@@ -35556,7 +35452,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="129" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B33" s="115"/>
       <c r="C33" s="115"/>
@@ -35567,7 +35463,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="128" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B34" s="115"/>
       <c r="C34" s="115"/>
@@ -35585,7 +35481,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="129" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B36" s="115"/>
       <c r="C36" s="115"/>
@@ -35596,7 +35492,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="130" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B37" s="115"/>
       <c r="C37" s="115"/>
@@ -35616,7 +35512,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="117" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B39" s="118"/>
       <c r="C39" s="118"/>
@@ -35627,7 +35523,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="128" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B40" s="115"/>
       <c r="C40" s="115"/>
@@ -35638,14 +35534,14 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="115" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B41" s="113">
         <f>'Heat pumps'!H25</f>
         <v>0.99</v>
       </c>
       <c r="C41" s="115" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D41" s="115"/>
       <c r="E41" s="115"/>
@@ -35654,7 +35550,7 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="115" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B42" s="124">
         <f>B41/B20-1</f>
@@ -35668,7 +35564,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="115" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B43" s="124">
         <f>B41/B21-1</f>
@@ -35682,12 +35578,12 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="116" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="45" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B47" s="46"/>
       <c r="C47" s="46"/>
@@ -35695,7 +35591,7 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B48" s="110">
         <v>0.56999999999999995</v>
@@ -35709,7 +35605,7 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B49" s="12">
         <f>1/B48</f>
@@ -35718,42 +35614,42 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="146" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="148" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="147" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B54" s="107" t="s">
+        <v>609</v>
+      </c>
+      <c r="C54" s="107" t="s">
+        <v>532</v>
+      </c>
+      <c r="D54" s="107" t="s">
+        <v>610</v>
+      </c>
+      <c r="E54" s="107" t="s">
         <v>611</v>
       </c>
-      <c r="C54" s="107" t="s">
-        <v>534</v>
-      </c>
-      <c r="D54" s="107" t="s">
+      <c r="F54" s="107" t="s">
         <v>612</v>
-      </c>
-      <c r="E54" s="107" t="s">
-        <v>613</v>
-      </c>
-      <c r="F54" s="107" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="15" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B55" s="23">
         <f>B15*$D$6*(1-'Combustion Efficiency'!$B$129)+C15*$D$7+D15*$D$8+E15*$D$9+F15*$D$10</f>
@@ -35777,7 +35673,7 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="15" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B56" s="23">
         <f>B16*$D$6*(1-'Combustion Efficiency'!$B$129)+C16*$D$7+D16*$D$8+E16*$D$9+F16*$D$10</f>
@@ -35801,7 +35697,7 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="15" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B57" s="120">
         <v>0.7</v>
@@ -35824,12 +35720,12 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="151" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="255">
       <c r="A60" s="155" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
   </sheetData>
@@ -35850,14 +35746,14 @@
     <row r="1" spans="2:14" ht="15.75" thickBot="1"/>
     <row r="2" spans="2:14" ht="30.95" customHeight="1">
       <c r="D2" s="131" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E2" s="131"/>
       <c r="F2" s="131"/>
       <c r="G2" s="131"/>
       <c r="H2" s="131"/>
       <c r="I2" s="163" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="J2" s="164"/>
       <c r="K2" s="164"/>
@@ -35866,48 +35762,48 @@
     </row>
     <row r="3" spans="2:14" ht="60">
       <c r="B3" t="s">
+        <v>563</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="D3" s="132" t="s">
+        <v>494</v>
+      </c>
+      <c r="E3" s="132" t="s">
+        <v>495</v>
+      </c>
+      <c r="F3" s="132" t="s">
+        <v>496</v>
+      </c>
+      <c r="G3" s="132" t="s">
+        <v>497</v>
+      </c>
+      <c r="H3" s="133" t="s">
+        <v>498</v>
+      </c>
+      <c r="I3" s="134" t="s">
+        <v>494</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="M3" s="135" t="s">
+        <v>498</v>
+      </c>
+      <c r="N3" s="136" t="s">
         <v>565</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>566</v>
-      </c>
-      <c r="D3" s="132" t="s">
-        <v>496</v>
-      </c>
-      <c r="E3" s="132" t="s">
-        <v>497</v>
-      </c>
-      <c r="F3" s="132" t="s">
-        <v>498</v>
-      </c>
-      <c r="G3" s="132" t="s">
-        <v>499</v>
-      </c>
-      <c r="H3" s="133" t="s">
-        <v>500</v>
-      </c>
-      <c r="I3" s="134" t="s">
-        <v>496</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>497</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>498</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="M3" s="135" t="s">
-        <v>500</v>
-      </c>
-      <c r="N3" s="136" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="4" spans="2:14">
       <c r="B4" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C4" s="137">
         <v>4.1094089371344421E-2</v>
@@ -35953,7 +35849,7 @@
     </row>
     <row r="5" spans="2:14">
       <c r="B5" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C5" s="137">
         <v>0</v>
@@ -35999,7 +35895,7 @@
     </row>
     <row r="6" spans="2:14">
       <c r="B6" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C6" s="137">
         <v>4.0805825486475107E-2</v>
@@ -36045,7 +35941,7 @@
     </row>
     <row r="7" spans="2:14">
       <c r="B7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C7" s="137">
         <v>2.3082653003295327E-2</v>
@@ -36091,7 +35987,7 @@
     </row>
     <row r="8" spans="2:14">
       <c r="B8" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C8" s="137">
         <v>9.7591784811817753E-2</v>
@@ -36137,7 +36033,7 @@
     </row>
     <row r="9" spans="2:14">
       <c r="B9" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C9" s="137">
         <v>3.2056865699710202E-3</v>
@@ -36183,7 +36079,7 @@
     </row>
     <row r="10" spans="2:14">
       <c r="B10" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C10" s="137">
         <v>5.8503779901971122E-2</v>
@@ -36229,7 +36125,7 @@
     </row>
     <row r="11" spans="2:14">
       <c r="B11" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C11" s="137">
         <v>0.17093361928399475</v>
@@ -36275,7 +36171,7 @@
     </row>
     <row r="12" spans="2:14">
       <c r="B12" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C12" s="137">
         <v>0.10696307521803304</v>
@@ -36321,7 +36217,7 @@
     </row>
     <row r="13" spans="2:14">
       <c r="B13" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C13" s="137">
         <v>0.24341846687979948</v>
@@ -36367,7 +36263,7 @@
     </row>
     <row r="14" spans="2:14">
       <c r="B14" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C14" s="137">
         <v>1.0578765680904366E-2</v>
@@ -36413,7 +36309,7 @@
     </row>
     <row r="15" spans="2:14">
       <c r="B15" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C15" s="137">
         <v>1.4853014440865727E-2</v>
@@ -36459,7 +36355,7 @@
     </row>
     <row r="16" spans="2:14">
       <c r="B16" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C16" s="137">
         <v>4.5141623428579913E-2</v>
@@ -36505,7 +36401,7 @@
     </row>
     <row r="17" spans="2:14">
       <c r="B17" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C17" s="137">
         <v>4.7764729892568206E-2</v>
@@ -36551,7 +36447,7 @@
     </row>
     <row r="18" spans="2:14">
       <c r="B18" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C18" s="137">
         <v>2.7782616939748844E-2</v>
@@ -36597,7 +36493,7 @@
     </row>
     <row r="19" spans="2:14">
       <c r="B19" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C19" s="137">
         <v>2.660719853075947E-2</v>
@@ -36643,7 +36539,7 @@
     </row>
     <row r="20" spans="2:14">
       <c r="B20" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C20" s="137">
         <v>2.030268160981646E-3</v>
@@ -36689,7 +36585,7 @@
     </row>
     <row r="21" spans="2:14">
       <c r="B21" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C21" s="137">
         <v>2.7782616939748843E-3</v>
@@ -36735,7 +36631,7 @@
     </row>
     <row r="22" spans="2:14">
       <c r="B22" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C22" s="137">
         <v>3.3125427889700541E-3</v>
@@ -36781,7 +36677,7 @@
     </row>
     <row r="23" spans="2:14">
       <c r="B23" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C23" s="137">
         <v>3.2056865699710202E-3</v>
@@ -36827,7 +36723,7 @@
     </row>
     <row r="24" spans="2:14">
       <c r="B24" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C24" s="137">
         <v>2.030268160981646E-3</v>
@@ -36873,7 +36769,7 @@
     </row>
     <row r="25" spans="2:14">
       <c r="B25" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C25" s="137">
         <v>4.4452187103598152E-3</v>
@@ -36919,7 +36815,7 @@
     </row>
     <row r="26" spans="2:14">
       <c r="B26" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C26" s="137">
         <v>0</v>
@@ -36965,7 +36861,7 @@
     </row>
     <row r="27" spans="2:14">
       <c r="B27" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C27" s="137">
         <v>6.4113731399420408E-4</v>
@@ -37011,7 +36907,7 @@
     </row>
     <row r="28" spans="2:14" ht="15.75" thickBot="1">
       <c r="B28" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C28" s="137">
         <v>2.3229687160638002E-2</v>
@@ -37057,7 +36953,7 @@
     </row>
     <row r="29" spans="2:14">
       <c r="C29" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
   </sheetData>
@@ -37103,15 +36999,15 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="2:13">
       <c r="D18" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F18">
         <v>2018</v>
@@ -37120,27 +37016,27 @@
         <v>2050</v>
       </c>
       <c r="K18" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" t="s">
         <v>34</v>
       </c>
-      <c r="C19" t="s">
+      <c r="E19" t="s">
         <v>35</v>
       </c>
-      <c r="D19" t="s">
+      <c r="F19" t="s">
         <v>36</v>
       </c>
-      <c r="E19" t="s">
-        <v>37</v>
-      </c>
-      <c r="F19" t="s">
-        <v>38</v>
-      </c>
       <c r="G19" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I19">
         <v>2021</v>
@@ -37149,18 +37045,18 @@
         <v>2050</v>
       </c>
       <c r="K19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D20">
         <v>0.218</v>
@@ -37193,10 +37089,10 @@
     </row>
     <row r="21" spans="2:13">
       <c r="B21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" t="s">
         <v>41</v>
-      </c>
-      <c r="C21" t="s">
-        <v>43</v>
       </c>
       <c r="D21">
         <v>2.1999999999999999E-2</v>
@@ -37229,10 +37125,10 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D22">
         <v>0.20399999999999999</v>
@@ -37265,10 +37161,10 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C23" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D23">
         <v>3.9E-2</v>
@@ -37301,10 +37197,10 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D24">
         <v>1.2999999999999999E-2</v>
@@ -37337,10 +37233,10 @@
     </row>
     <row r="25" spans="2:13">
       <c r="B25" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D25">
         <v>0.19900000000000001</v>
@@ -37373,10 +37269,10 @@
     </row>
     <row r="26" spans="2:13">
       <c r="B26" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D26">
         <v>1E-3</v>
@@ -37409,10 +37305,10 @@
     </row>
     <row r="27" spans="2:13">
       <c r="B27" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D27">
         <v>1.0999999999999999E-2</v>
@@ -37445,10 +37341,10 @@
     </row>
     <row r="28" spans="2:13">
       <c r="B28" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D28">
         <v>7.0000000000000001E-3</v>
@@ -37501,39 +37397,39 @@
   <sheetData>
     <row r="2" spans="8:15">
       <c r="H2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="8:15">
       <c r="H3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="8:15" s="9" customFormat="1" ht="45">
       <c r="I4" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="8:15">
       <c r="L5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="8:15">
       <c r="I6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J6">
         <v>83</v>
@@ -37542,7 +37438,7 @@
         <v>82</v>
       </c>
       <c r="L6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="M6">
         <v>90.1</v>
@@ -37557,7 +37453,7 @@
     </row>
     <row r="7" spans="8:15">
       <c r="I7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J7">
         <v>89</v>
@@ -37566,7 +37462,7 @@
         <v>89</v>
       </c>
       <c r="L7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M7">
         <v>93.1</v>
@@ -37581,7 +37477,7 @@
     </row>
     <row r="8" spans="8:15">
       <c r="I8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J8">
         <v>92</v>
@@ -37590,7 +37486,7 @@
         <v>91</v>
       </c>
       <c r="L8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M8">
         <v>94.7</v>
@@ -37605,7 +37501,7 @@
     </row>
     <row r="9" spans="8:15">
       <c r="I9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J9">
         <v>93</v>
@@ -37614,7 +37510,7 @@
         <v>92</v>
       </c>
       <c r="L9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M9">
         <v>95.9</v>
@@ -37629,7 +37525,7 @@
     </row>
     <row r="10" spans="8:15">
       <c r="I10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J10">
         <v>93</v>
@@ -37638,7 +37534,7 @@
         <v>93</v>
       </c>
       <c r="L10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M10">
         <v>96.2</v>
@@ -37653,7 +37549,7 @@
     </row>
     <row r="11" spans="8:15">
       <c r="I11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J11">
         <v>93</v>
@@ -37662,7 +37558,7 @@
         <v>94</v>
       </c>
       <c r="L11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="M11">
         <v>96.2</v>
@@ -37677,7 +37573,7 @@
     </row>
     <row r="12" spans="8:15">
       <c r="I12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J12">
         <v>93</v>
@@ -37696,7 +37592,7 @@
     </row>
     <row r="13" spans="8:15">
       <c r="I13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J13">
         <v>92</v>
@@ -37715,7 +37611,7 @@
     </row>
     <row r="14" spans="8:15">
       <c r="I14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J14">
         <v>86</v>
@@ -37734,13 +37630,13 @@
     </row>
     <row r="15" spans="8:15">
       <c r="I15" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J15">
         <v>91</v>
       </c>
       <c r="K15" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M15">
         <f>M14</f>
@@ -37753,23 +37649,23 @@
     </row>
     <row r="17" spans="9:12">
       <c r="J17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="9:12">
       <c r="I18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J18" s="18">
         <v>25.980397752045299</v>
       </c>
       <c r="L18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="9:12">
       <c r="I19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J19" s="18">
         <v>67.647063795395397</v>
@@ -37780,18 +37676,18 @@
     </row>
     <row r="20" spans="9:12">
       <c r="I20" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J20" s="18">
         <v>86.928108261286297</v>
       </c>
       <c r="L20" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="9:12">
       <c r="I21" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J21" s="18">
         <v>71.895427750300499</v>
@@ -37799,7 +37695,7 @@
     </row>
     <row r="22" spans="9:12">
       <c r="I22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J22" s="18">
         <v>64.379085998847998</v>
@@ -37807,7 +37703,7 @@
     </row>
     <row r="23" spans="9:12">
       <c r="I23" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J23" s="18">
         <v>94.281049327759803</v>
@@ -37815,7 +37711,7 @@
     </row>
     <row r="24" spans="9:12">
       <c r="I24" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J24" s="18">
         <v>62.908497785553301</v>
@@ -37823,7 +37719,7 @@
     </row>
     <row r="25" spans="9:12">
       <c r="I25" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J25" s="18">
         <v>34.803927031813501</v>
@@ -37831,7 +37727,7 @@
     </row>
     <row r="26" spans="9:12">
       <c r="I26" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J26" s="18">
         <v>17.6470525756977</v>
@@ -37839,7 +37735,7 @@
     </row>
     <row r="27" spans="9:12">
       <c r="I27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J27" s="18">
         <v>17.156856504599499</v>
@@ -37847,10 +37743,10 @@
     </row>
     <row r="29" spans="9:12">
       <c r="J29" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" spans="9:12">
@@ -37875,7 +37771,7 @@
     </row>
     <row r="34" spans="10:11">
       <c r="J34" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="35" spans="10:11">
@@ -37883,7 +37779,7 @@
         <v>0.4</v>
       </c>
       <c r="K35" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36" spans="10:11">
@@ -37892,7 +37788,7 @@
         <v>2.1414913957934991</v>
       </c>
       <c r="K36" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -37908,21 +37804,21 @@
   <sheetData>
     <row r="24" spans="2:8">
       <c r="B24" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C24">
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H24" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="25" spans="2:8">
       <c r="B25" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C25">
         <f>1/C24</f>
@@ -37934,7 +37830,7 @@
     </row>
     <row r="26" spans="2:8">
       <c r="B26" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C26">
         <v>5</v>
@@ -37942,19 +37838,19 @@
     </row>
     <row r="27" spans="2:8">
       <c r="B27" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C27">
         <f>1/C26</f>
         <v>0.2</v>
       </c>
       <c r="D27" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30" spans="2:8">
       <c r="B30" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C30" s="52">
         <v>3</v>
@@ -37962,7 +37858,7 @@
     </row>
     <row r="31" spans="2:8">
       <c r="B31" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C31" s="12">
         <f>IFERROR(1/C30,"")</f>
@@ -37993,11 +37889,11 @@
   <sheetData>
     <row r="1" spans="1:13" ht="11.25" customHeight="1">
       <c r="A1" s="56" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B1" s="57"/>
       <c r="C1" s="159" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D1" s="160"/>
       <c r="E1" s="160"/>
@@ -38012,7 +37908,7 @@
     </row>
     <row r="2" spans="1:13" ht="11.25" customHeight="1">
       <c r="A2" s="60" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B2" s="61"/>
       <c r="C2" s="58">
@@ -38043,57 +37939,57 @@
         <v>2050</v>
       </c>
       <c r="L2" s="58" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="M2" s="58" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="11.25" customHeight="1" thickBot="1">
       <c r="A3" s="62" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B3" s="63"/>
       <c r="C3" s="64" t="s">
+        <v>321</v>
+      </c>
+      <c r="D3" s="64" t="s">
+        <v>321</v>
+      </c>
+      <c r="E3" s="64" t="s">
+        <v>321</v>
+      </c>
+      <c r="F3" s="64" t="s">
+        <v>321</v>
+      </c>
+      <c r="G3" s="64" t="s">
+        <v>321</v>
+      </c>
+      <c r="H3" s="64" t="s">
+        <v>322</v>
+      </c>
+      <c r="I3" s="64" t="s">
         <v>323</v>
       </c>
-      <c r="D3" s="64" t="s">
+      <c r="J3" s="64" t="s">
+        <v>322</v>
+      </c>
+      <c r="K3" s="64" t="s">
         <v>323</v>
       </c>
-      <c r="E3" s="64" t="s">
-        <v>323</v>
-      </c>
-      <c r="F3" s="64" t="s">
-        <v>323</v>
-      </c>
-      <c r="G3" s="64" t="s">
-        <v>323</v>
-      </c>
-      <c r="H3" s="64" t="s">
-        <v>324</v>
-      </c>
-      <c r="I3" s="64" t="s">
-        <v>325</v>
-      </c>
-      <c r="J3" s="64" t="s">
-        <v>324</v>
-      </c>
-      <c r="K3" s="64" t="s">
-        <v>325</v>
-      </c>
       <c r="L3" s="64" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="M3" s="64" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="11.25" customHeight="1">
       <c r="A4" s="65" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B4" s="66" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C4" s="58"/>
       <c r="D4" s="58"/>
@@ -38109,7 +38005,7 @@
     </row>
     <row r="5" spans="1:13" ht="11.25" customHeight="1">
       <c r="A5" s="67" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B5" s="68"/>
       <c r="E5" s="69"/>
@@ -38120,7 +38016,7 @@
     </row>
     <row r="6" spans="1:13" ht="11.25" customHeight="1">
       <c r="B6" s="71" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C6" s="72">
         <v>3</v>
@@ -38150,15 +38046,15 @@
         <v>5</v>
       </c>
       <c r="L6" s="73" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="M6" s="72" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="11.25" customHeight="1">
       <c r="B7" s="71" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C7" s="74">
         <v>3.35</v>
@@ -38193,15 +38089,15 @@
         <v>3.6042577200000001</v>
       </c>
       <c r="L7" s="73" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="M7" s="72" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="11.25" customHeight="1">
       <c r="B8" s="71" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C8" s="74">
         <f>C7-5%</f>
@@ -38240,13 +38136,13 @@
         <v>3.5542577200000003</v>
       </c>
       <c r="L8" s="73" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="M8" s="72"/>
     </row>
     <row r="9" spans="1:13" ht="11.25" customHeight="1">
       <c r="B9" s="71" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C9" s="74">
         <v>0.01</v>
@@ -38282,7 +38178,7 @@
     </row>
     <row r="10" spans="1:13" ht="11.25" customHeight="1">
       <c r="B10" s="71" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C10" s="74">
         <v>0</v>
@@ -38312,7 +38208,7 @@
         <v>0.01</v>
       </c>
       <c r="L10" s="73" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="M10" s="72">
         <v>2</v>
@@ -38320,7 +38216,7 @@
     </row>
     <row r="11" spans="1:13" ht="11.25" customHeight="1">
       <c r="B11" s="71" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C11" s="72">
         <v>1</v>
@@ -38356,7 +38252,7 @@
     </row>
     <row r="12" spans="1:13" ht="11.25" customHeight="1">
       <c r="B12" s="71" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C12" s="72">
         <v>25</v>
@@ -38392,7 +38288,7 @@
     </row>
     <row r="13" spans="1:13" ht="11.25" customHeight="1">
       <c r="B13" s="71" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C13" s="72">
         <v>0.5</v>
@@ -38428,7 +38324,7 @@
     </row>
     <row r="14" spans="1:13" ht="11.25" customHeight="1">
       <c r="A14" s="70" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B14" s="75"/>
       <c r="C14" s="76"/>
@@ -38445,7 +38341,7 @@
     </row>
     <row r="15" spans="1:13" ht="11.25" customHeight="1">
       <c r="B15" s="71" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C15" s="74">
         <v>0.25</v>
@@ -38481,7 +38377,7 @@
     </row>
     <row r="16" spans="1:13" ht="11.25" customHeight="1">
       <c r="B16" s="71" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C16" s="77">
         <v>0.1</v>
@@ -38517,7 +38413,7 @@
     </row>
     <row r="17" spans="1:13" ht="11.25" customHeight="1">
       <c r="B17" s="71" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C17" s="77">
         <v>1</v>
@@ -38553,7 +38449,7 @@
     </row>
     <row r="18" spans="1:13" ht="11.25" customHeight="1">
       <c r="A18" s="70" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B18" s="75"/>
       <c r="C18" s="76"/>
@@ -38570,7 +38466,7 @@
     </row>
     <row r="19" spans="1:13" ht="11.25" customHeight="1">
       <c r="B19" s="71" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C19" s="73">
         <v>0.95</v>
@@ -38606,7 +38502,7 @@
     </row>
     <row r="20" spans="1:13" ht="11.25" customHeight="1">
       <c r="B20" s="71" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C20" s="78">
         <v>0.4</v>
@@ -38624,7 +38520,7 @@
         <v>0.4</v>
       </c>
       <c r="L20" s="73" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="M20" s="73">
         <v>2</v>
@@ -38632,7 +38528,7 @@
     </row>
     <row r="21" spans="1:13" ht="11.25" customHeight="1">
       <c r="B21" s="71" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C21" s="78">
         <v>0.6</v>
@@ -38650,7 +38546,7 @@
         <v>0.6</v>
       </c>
       <c r="L21" s="73" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="M21" s="73">
         <v>2</v>
@@ -38658,7 +38554,7 @@
     </row>
     <row r="22" spans="1:13" ht="11.25" customHeight="1">
       <c r="B22" s="71" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C22" s="79">
         <v>2127</v>
@@ -38694,7 +38590,7 @@
     </row>
     <row r="23" spans="1:13" ht="11.25" customHeight="1">
       <c r="B23" s="71" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C23" s="82">
         <v>3.07</v>
@@ -38730,7 +38626,7 @@
     </row>
     <row r="24" spans="1:13" ht="11.25" customHeight="1">
       <c r="A24" s="70" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B24" s="75"/>
       <c r="C24" s="76"/>
@@ -38747,7 +38643,7 @@
     </row>
     <row r="25" spans="1:13" ht="11.25" customHeight="1">
       <c r="B25" s="71" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C25" s="83">
         <f>C19*0.2</f>
@@ -38774,35 +38670,35 @@
       <c r="J25" s="70"/>
       <c r="K25" s="70"/>
       <c r="L25" s="73" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="M25" s="73"/>
     </row>
     <row r="26" spans="1:13" ht="11.25" customHeight="1">
       <c r="B26" s="71" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C26" s="73" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D26" s="73" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E26" s="73" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F26" s="73" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G26" s="73" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L26" s="73"/>
       <c r="M26" s="73"/>
     </row>
     <row r="27" spans="1:13" ht="11.25" customHeight="1">
       <c r="B27" s="71" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C27" s="73">
         <v>10</v>
@@ -38824,7 +38720,7 @@
     </row>
     <row r="28" spans="1:13" ht="11.25" customHeight="1">
       <c r="B28" s="71" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C28" s="73">
         <v>15</v>
@@ -38842,13 +38738,13 @@
         <v>15</v>
       </c>
       <c r="L28" s="73" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="M28" s="73"/>
     </row>
     <row r="29" spans="1:13" ht="11.25" customHeight="1">
       <c r="B29" s="71" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C29" s="73">
         <v>5</v>
@@ -38866,13 +38762,13 @@
         <v>5</v>
       </c>
       <c r="L29" s="73" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="M29" s="73"/>
     </row>
     <row r="30" spans="1:13" ht="11.25" customHeight="1">
       <c r="B30" s="71" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C30" s="84">
         <f>C6-C6/(C7/100)</f>
@@ -38929,7 +38825,7 @@
     </row>
     <row r="33" spans="1:13" ht="11.25" customHeight="1">
       <c r="A33" s="87" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C33" s="86"/>
       <c r="D33" s="86"/>
@@ -38945,10 +38841,10 @@
     </row>
     <row r="34" spans="1:13" ht="11.25" customHeight="1">
       <c r="A34" s="88" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B34" s="86" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C34" s="86"/>
       <c r="D34" s="86"/>
@@ -38964,10 +38860,10 @@
     </row>
     <row r="35" spans="1:13" ht="11.25" customHeight="1">
       <c r="A35" s="88" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B35" s="86" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C35" s="86"/>
       <c r="D35" s="86"/>
@@ -38983,10 +38879,10 @@
     </row>
     <row r="36" spans="1:13" ht="11.25" customHeight="1">
       <c r="A36" s="88" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B36" s="86" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C36" s="86"/>
       <c r="D36" s="86"/>
@@ -39002,10 +38898,10 @@
     </row>
     <row r="37" spans="1:13" ht="11.25" customHeight="1">
       <c r="A37" s="88" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B37" s="86" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D37" s="86"/>
       <c r="E37" s="86"/>
@@ -39020,10 +38916,10 @@
     </row>
     <row r="38" spans="1:13" ht="11.25" customHeight="1">
       <c r="A38" s="88" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B38" s="86" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C38" s="86"/>
       <c r="D38" s="86"/>
@@ -39039,10 +38935,10 @@
     </row>
     <row r="39" spans="1:13" ht="11.25" customHeight="1">
       <c r="A39" s="88" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B39" s="86" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C39" s="86"/>
       <c r="D39" s="86"/>
@@ -39058,10 +38954,10 @@
     </row>
     <row r="40" spans="1:13" ht="11.25" customHeight="1">
       <c r="A40" s="88" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B40" s="86" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C40" s="86"/>
       <c r="D40" s="86"/>
@@ -39077,10 +38973,10 @@
     </row>
     <row r="41" spans="1:13" ht="11.25" customHeight="1">
       <c r="A41" s="88" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B41" s="86" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C41" s="86"/>
       <c r="D41" s="86"/>
@@ -39096,10 +38992,10 @@
     </row>
     <row r="42" spans="1:13" ht="11.25" customHeight="1">
       <c r="A42" s="88" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B42" s="86" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C42" s="86"/>
       <c r="D42" s="86"/>
@@ -39118,7 +39014,7 @@
     </row>
     <row r="44" spans="1:13" ht="11.25" customHeight="1">
       <c r="A44" s="67" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B44" s="86"/>
       <c r="C44" s="86"/>
@@ -39128,7 +39024,7 @@
         <v>1</v>
       </c>
       <c r="B45" s="86" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C45" s="86"/>
     </row>
@@ -39137,7 +39033,7 @@
         <v>2</v>
       </c>
       <c r="B46" s="86" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C46" s="86"/>
     </row>
@@ -39146,7 +39042,7 @@
         <v>3</v>
       </c>
       <c r="B47" s="86" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -39174,11 +39070,11 @@
   <sheetData>
     <row r="1" spans="1:13" ht="11.25" customHeight="1">
       <c r="A1" s="56" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B1" s="89"/>
       <c r="C1" s="161" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D1" s="160"/>
       <c r="E1" s="160"/>
@@ -39193,7 +39089,7 @@
     </row>
     <row r="2" spans="1:13" ht="11.25" customHeight="1">
       <c r="A2" s="60" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B2" s="60"/>
       <c r="C2" s="58">
@@ -39224,57 +39120,57 @@
         <v>2050</v>
       </c>
       <c r="L2" s="58" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="M2" s="58" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="11.25" customHeight="1" thickBot="1">
       <c r="A3" s="62" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B3" s="62"/>
       <c r="C3" s="64" t="s">
+        <v>321</v>
+      </c>
+      <c r="D3" s="64" t="s">
+        <v>321</v>
+      </c>
+      <c r="E3" s="64" t="s">
+        <v>321</v>
+      </c>
+      <c r="F3" s="64" t="s">
+        <v>321</v>
+      </c>
+      <c r="G3" s="64" t="s">
+        <v>321</v>
+      </c>
+      <c r="H3" s="64" t="s">
+        <v>322</v>
+      </c>
+      <c r="I3" s="64" t="s">
         <v>323</v>
       </c>
-      <c r="D3" s="64" t="s">
+      <c r="J3" s="64" t="s">
+        <v>322</v>
+      </c>
+      <c r="K3" s="64" t="s">
         <v>323</v>
       </c>
-      <c r="E3" s="64" t="s">
-        <v>323</v>
-      </c>
-      <c r="F3" s="64" t="s">
-        <v>323</v>
-      </c>
-      <c r="G3" s="64" t="s">
-        <v>323</v>
-      </c>
-      <c r="H3" s="64" t="s">
-        <v>324</v>
-      </c>
-      <c r="I3" s="64" t="s">
-        <v>325</v>
-      </c>
-      <c r="J3" s="64" t="s">
-        <v>324</v>
-      </c>
-      <c r="K3" s="64" t="s">
-        <v>325</v>
-      </c>
       <c r="L3" s="64" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="M3" s="64" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="11.25" customHeight="1">
       <c r="A4" s="65" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B4" s="65" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C4" s="58"/>
       <c r="D4" s="58"/>
@@ -39290,7 +39186,7 @@
     </row>
     <row r="5" spans="1:13" ht="11.25" customHeight="1">
       <c r="A5" s="87" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C5" s="91"/>
       <c r="D5" s="91"/>
@@ -39307,7 +39203,7 @@
     <row r="6" spans="1:13" ht="11.25" customHeight="1">
       <c r="A6" s="87"/>
       <c r="B6" s="90" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C6" s="92">
         <v>2</v>
@@ -39337,7 +39233,7 @@
         <v>100</v>
       </c>
       <c r="L6" s="92" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="M6" s="92">
         <v>4</v>
@@ -39346,7 +39242,7 @@
     <row r="7" spans="1:13" ht="11.25" customHeight="1">
       <c r="A7" s="87"/>
       <c r="B7" s="90" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C7" s="93">
         <v>2.75</v>
@@ -39376,7 +39272,7 @@
         <v>4.5</v>
       </c>
       <c r="L7" s="92" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="M7" s="92">
         <v>1</v>
@@ -39385,7 +39281,7 @@
     <row r="8" spans="1:13" ht="11.25" customHeight="1">
       <c r="A8" s="87"/>
       <c r="B8" s="90" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C8" s="93">
         <v>2.7</v>
@@ -39420,7 +39316,7 @@
     <row r="9" spans="1:13" ht="11.25" customHeight="1">
       <c r="A9" s="87"/>
       <c r="B9" s="90" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C9" s="93">
         <v>0.02</v>
@@ -39457,7 +39353,7 @@
     <row r="10" spans="1:13" ht="11.25" customHeight="1">
       <c r="A10" s="94"/>
       <c r="B10" s="94" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C10" s="95">
         <v>0</v>
@@ -39494,7 +39390,7 @@
     <row r="11" spans="1:13" ht="11.25" customHeight="1">
       <c r="A11" s="87"/>
       <c r="B11" s="90" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C11" s="96">
         <v>0.5</v>
@@ -39531,7 +39427,7 @@
     <row r="12" spans="1:13" ht="11.25" customHeight="1">
       <c r="A12" s="87"/>
       <c r="B12" s="90" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C12" s="92">
         <v>20</v>
@@ -39561,7 +39457,7 @@
         <v>30</v>
       </c>
       <c r="L12" s="92" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="M12" s="92">
         <v>4</v>
@@ -39570,7 +39466,7 @@
     <row r="13" spans="1:13" ht="11.25" customHeight="1">
       <c r="A13" s="87"/>
       <c r="B13" s="90" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C13" s="96">
         <v>0.6</v>
@@ -39600,7 +39496,7 @@
         <v>0.8</v>
       </c>
       <c r="L13" s="91" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="M13" s="92">
         <v>4</v>
@@ -39609,7 +39505,7 @@
     <row r="14" spans="1:13" ht="11.25" customHeight="1">
       <c r="A14" s="87"/>
       <c r="B14" s="90" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C14" s="97">
         <v>0.03</v>
@@ -39643,7 +39539,7 @@
     </row>
     <row r="15" spans="1:13" ht="11.25" customHeight="1">
       <c r="A15" s="87" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C15" s="92"/>
       <c r="D15" s="92"/>
@@ -39660,7 +39556,7 @@
     <row r="16" spans="1:13" ht="11.25" customHeight="1">
       <c r="A16" s="94"/>
       <c r="B16" s="94" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C16" s="93">
         <v>0.05</v>
@@ -39695,7 +39591,7 @@
     <row r="17" spans="1:13" ht="11.25" customHeight="1">
       <c r="A17" s="94"/>
       <c r="B17" s="94" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C17" s="93">
         <v>0.1</v>
@@ -39730,7 +39626,7 @@
     <row r="18" spans="1:13" ht="11.25" customHeight="1">
       <c r="A18" s="94"/>
       <c r="B18" s="94" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C18" s="93">
         <v>0.25</v>
@@ -39760,7 +39656,7 @@
         <v>0.5</v>
       </c>
       <c r="L18" s="92" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="M18" s="92">
         <v>4</v>
@@ -39769,7 +39665,7 @@
     <row r="19" spans="1:13" ht="11.25" customHeight="1">
       <c r="A19" s="87"/>
       <c r="B19" s="90" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C19" s="92">
         <v>0.25</v>
@@ -39806,7 +39702,7 @@
     <row r="20" spans="1:13" ht="11.25" customHeight="1">
       <c r="A20" s="87"/>
       <c r="B20" s="90" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C20" s="92">
         <v>1</v>
@@ -39842,7 +39738,7 @@
     </row>
     <row r="21" spans="1:13" ht="11.25" customHeight="1">
       <c r="A21" s="87" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C21" s="92"/>
       <c r="D21" s="92"/>
@@ -39859,7 +39755,7 @@
     <row r="22" spans="1:13" ht="11.25" customHeight="1">
       <c r="A22" s="87"/>
       <c r="B22" s="90" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C22" s="97">
         <v>1.55</v>
@@ -39889,14 +39785,14 @@
         <v>1.65</v>
       </c>
       <c r="L22" s="92" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="M22" s="92"/>
     </row>
     <row r="23" spans="1:13" ht="11.25" customHeight="1">
       <c r="A23" s="87"/>
       <c r="B23" s="90" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C23" s="98">
         <v>0.4</v>
@@ -39926,7 +39822,7 @@
         <v>0.7</v>
       </c>
       <c r="L23" s="92" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="M23" s="92">
         <v>1</v>
@@ -39935,7 +39831,7 @@
     <row r="24" spans="1:13" ht="11.25" customHeight="1">
       <c r="A24" s="87"/>
       <c r="B24" s="90" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C24" s="98">
         <v>0.6</v>
@@ -39965,7 +39861,7 @@
         <v>0.75</v>
       </c>
       <c r="L24" s="92" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="M24" s="92">
         <v>3</v>
@@ -39974,7 +39870,7 @@
     <row r="25" spans="1:13" ht="11.25" customHeight="1">
       <c r="A25" s="87"/>
       <c r="B25" s="90" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C25" s="99">
         <v>2494</v>
@@ -40003,7 +39899,7 @@
     <row r="26" spans="1:13" ht="11.25" customHeight="1">
       <c r="A26" s="87"/>
       <c r="B26" s="90" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C26" s="97">
         <v>3.6</v>
@@ -40031,7 +39927,7 @@
     </row>
     <row r="27" spans="1:13" ht="11.25" customHeight="1">
       <c r="A27" s="87" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C27" s="92"/>
       <c r="D27" s="92"/>
@@ -40048,7 +39944,7 @@
     <row r="28" spans="1:13" ht="11.25" customHeight="1">
       <c r="A28" s="87"/>
       <c r="B28" s="90" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C28" s="99"/>
       <c r="D28" s="99"/>
@@ -40065,7 +39961,7 @@
     <row r="29" spans="1:13" ht="11.25" customHeight="1">
       <c r="A29" s="87"/>
       <c r="B29" s="90" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C29" s="92">
         <v>0.23</v>
@@ -40087,14 +39983,14 @@
       <c r="J29" s="92"/>
       <c r="K29" s="92"/>
       <c r="L29" s="92" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="M29" s="92"/>
     </row>
     <row r="30" spans="1:13" ht="11.25" customHeight="1">
       <c r="A30" s="87"/>
       <c r="B30" s="90" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C30" s="98">
         <v>-0.15</v>
@@ -40125,13 +40021,13 @@
       </c>
       <c r="L30" s="92"/>
       <c r="M30" s="92" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="11.25" customHeight="1">
       <c r="A31" s="87"/>
       <c r="B31" s="90" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C31" s="100">
         <v>0.2</v>
@@ -40162,13 +40058,13 @@
       </c>
       <c r="L31" s="92"/>
       <c r="M31" s="92" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="11.25" customHeight="1">
       <c r="A32" s="87"/>
       <c r="B32" s="101" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C32" s="102">
         <f>MROUND(C22*C23*0.3,0.05)</f>
@@ -40208,13 +40104,13 @@
       </c>
       <c r="L32" s="92"/>
       <c r="M32" s="92" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="11.25" customHeight="1">
       <c r="A33" s="87"/>
       <c r="B33" s="90" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C33" s="93">
         <v>4.45</v>
@@ -40245,13 +40141,13 @@
       </c>
       <c r="L33" s="92"/>
       <c r="M33" s="92" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="11.25" customHeight="1">
       <c r="A34" s="103"/>
       <c r="B34" s="90" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C34" s="93">
         <v>2.4</v>
@@ -40282,13 +40178,13 @@
       </c>
       <c r="L34" s="92"/>
       <c r="M34" s="92" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="11.25" customHeight="1">
       <c r="A35" s="103"/>
       <c r="B35" s="90" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C35" s="93">
         <v>2.0499999999999998</v>
@@ -40319,7 +40215,7 @@
       </c>
       <c r="L35" s="92"/>
       <c r="M35" s="92" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="11.25" customHeight="1" thickBot="1">
@@ -40352,79 +40248,79 @@
     </row>
     <row r="38" spans="1:13" ht="11.25" customHeight="1">
       <c r="A38" s="87" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="39" spans="1:13" s="106" customFormat="1" ht="11.25" customHeight="1">
       <c r="A39" s="88" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B39" s="106" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="40" spans="1:13" s="106" customFormat="1" ht="11.25" customHeight="1">
       <c r="A40" s="88" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B40" s="106" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="41" spans="1:13" s="106" customFormat="1" ht="11.25" customHeight="1">
       <c r="A41" s="88" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B41" s="106" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="42" spans="1:13" s="106" customFormat="1" ht="11.25" customHeight="1">
       <c r="A42" s="88" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B42" s="90" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="43" spans="1:13" s="106" customFormat="1" ht="11.25" customHeight="1">
       <c r="A43" s="88" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B43" s="106" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="11.25" customHeight="1">
       <c r="A44" s="88" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B44" s="106" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="11.25" customHeight="1">
       <c r="A45" s="88" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B45" s="106" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="11.25" customHeight="1">
       <c r="A46" s="88" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B46" s="106" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="11.25" customHeight="1">
       <c r="A47" s="88" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B47" s="106" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="11.25" customHeight="1">
@@ -40433,7 +40329,7 @@
     </row>
     <row r="49" spans="1:2" s="106" customFormat="1" ht="11.25" customHeight="1">
       <c r="A49" s="87" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B49" s="90"/>
     </row>
@@ -40442,7 +40338,7 @@
         <v>1</v>
       </c>
       <c r="B50" s="106" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="51" spans="1:2" s="106" customFormat="1" ht="11.25" customHeight="1">
@@ -40450,7 +40346,7 @@
         <v>2</v>
       </c>
       <c r="B51" s="106" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="52" spans="1:2" s="106" customFormat="1" ht="11.25" customHeight="1">
@@ -40458,7 +40354,7 @@
         <v>3</v>
       </c>
       <c r="B52" s="90" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="11.25" customHeight="1">
@@ -40466,7 +40362,7 @@
         <v>4</v>
       </c>
       <c r="B53" s="90" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="11.25" customHeight="1">
@@ -40908,15 +40804,15 @@
   <sheetData>
     <row r="2" spans="2:11">
       <c r="B2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="2:11">
       <c r="J3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="K3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="2:11">
@@ -40964,39 +40860,39 @@
     </row>
     <row r="18" spans="2:14">
       <c r="B18" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="2:14">
       <c r="B19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="2:14">
       <c r="I21" s="19" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="2:14">
       <c r="J23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K23" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="L23" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="M23" t="s">
+        <v>139</v>
+      </c>
+      <c r="N23" t="s">
         <v>141</v>
-      </c>
-      <c r="N23" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="24" spans="2:14">
       <c r="J24" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K24">
         <v>0.79</v>
@@ -41016,7 +40912,7 @@
     </row>
     <row r="25" spans="2:14">
       <c r="J25" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K25">
         <v>0.79</v>
@@ -41028,7 +40924,7 @@
     </row>
     <row r="26" spans="2:14">
       <c r="J26" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="K26">
         <v>0.71699999999999997</v>
@@ -41040,7 +40936,7 @@
     </row>
     <row r="27" spans="2:14">
       <c r="J27" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K27">
         <v>0.63900000000000001</v>
@@ -41052,12 +40948,12 @@
     </row>
     <row r="28" spans="2:14">
       <c r="J28" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="2:14">
       <c r="J29" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K29">
         <v>0.70299999999999996</v>
@@ -41069,7 +40965,7 @@
     </row>
     <row r="30" spans="2:14">
       <c r="J30" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="K30">
         <v>0.63400000000000001</v>
@@ -41081,7 +40977,7 @@
     </row>
     <row r="31" spans="2:14">
       <c r="J31" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K31">
         <v>0.57599999999999996</v>
@@ -41093,7 +40989,7 @@
     </row>
     <row r="32" spans="2:14">
       <c r="J32" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K32">
         <v>0.57599999999999996</v>
@@ -41105,17 +41001,17 @@
     </row>
     <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="37" spans="2:2">
@@ -41137,7 +41033,7 @@
   <sheetData>
     <row r="2" spans="1:9">
       <c r="A2" s="22" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B2" s="21"/>
       <c r="C2" s="21"/>
@@ -41150,24 +41046,24 @@
     </row>
     <row r="3" spans="1:9">
       <c r="B3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B4">
         <v>425</v>
       </c>
       <c r="C4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E4">
         <f>AVERAGE(B4:B6)</f>
@@ -41180,40 +41076,40 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B5">
         <v>440</v>
       </c>
       <c r="C5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B6">
         <v>400</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="B7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B8">
         <v>361</v>
       </c>
       <c r="C8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E8">
         <f>AVERAGE(B8:B10)</f>
@@ -41222,29 +41118,29 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B9">
         <v>350</v>
       </c>
       <c r="C9" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B10">
         <v>300</v>
       </c>
       <c r="C10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="22" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B12" s="21"/>
       <c r="C12" s="21"/>
@@ -41257,23 +41153,23 @@
     </row>
     <row r="13" spans="1:9">
       <c r="B13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B14" s="23">
         <v>0.504</v>
       </c>
       <c r="G14" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="B15" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G15">
         <f>1/B16</f>
@@ -41282,7 +41178,7 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B16" s="23">
         <v>0.55100000000000005</v>
@@ -41290,7 +41186,7 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="22" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B18" s="22"/>
       <c r="C18" s="22"/>
@@ -41303,10 +41199,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G19" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -41314,7 +41210,7 @@
         <v>1100</v>
       </c>
       <c r="C20" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G20">
         <f>B22/B22</f>
@@ -41323,10 +41219,10 @@
     </row>
     <row r="21" spans="1:9">
       <c r="B21" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G21" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -41334,7 +41230,7 @@
         <v>793</v>
       </c>
       <c r="C22" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G22">
         <f>1/G20</f>
@@ -41343,63 +41239,63 @@
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="109" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B28">
         <f>E4</f>
         <v>421.66666666666669</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B29">
         <f>B8</f>
         <v>361</v>
       </c>
       <c r="C29" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B30">
         <f>B10</f>
         <v>300</v>
       </c>
       <c r="C30" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -41412,7 +41308,7 @@
         <v>1.1680517082179132</v>
       </c>
       <c r="C34" s="108" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -41421,19 +41317,19 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B38" s="12">
         <f>B28/B30</f>
         <v>1.4055555555555557</v>
       </c>
       <c r="C38" s="108" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
   </sheetData>
@@ -41449,12 +41345,12 @@
   <sheetData>
     <row r="2" spans="1:2">
       <c r="B2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B3" s="11">
         <v>0.61</v>
@@ -41462,12 +41358,12 @@
     </row>
     <row r="4" spans="1:2">
       <c r="B4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B5" s="11">
         <v>0.7</v>
@@ -41475,12 +41371,12 @@
     </row>
     <row r="7" spans="1:2">
       <c r="B7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B8" s="11">
         <v>0.61</v>
@@ -41488,12 +41384,12 @@
     </row>
     <row r="9" spans="1:2">
       <c r="B9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B10" s="11">
         <v>0.72</v>
@@ -41501,7 +41397,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B12" s="11">
         <f>AVERAGE(B10,B5)</f>
@@ -41510,7 +41406,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B13">
         <f>1/B12</f>
